--- a/reports/Debug-snowbowl-20251216/For The Week Ending (Prior Year)_PayrollHistory.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Week Ending (Prior Year)_PayrollHistory.xlsx
@@ -22,118 +22,118 @@
     <t>total</t>
   </si>
   <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D9007</t>
+  </si>
+  <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D6721</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D9012</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5112</t>
+  </si>
+  <si>
+    <t>D6760</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
     <t>D8030</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D9007</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5112</t>
-  </si>
-  <si>
-    <t>D6760</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D6721</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D9012</t>
   </si>
 </sst>
 </file>
@@ -516,7 +516,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>1538.46</v>
+        <v>3776.20</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -524,7 +524,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>1794.54</v>
+        <v>791.10</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -532,7 +532,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>1404.80</v>
+        <v>316.32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>417.16</v>
+        <v>2392.64</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -548,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>581.46</v>
+        <v>110.82</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>604.40</v>
+        <v>1071.60</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -564,7 +564,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>5573.19</v>
+        <v>1721.51</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -572,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>2949.30</v>
+        <v>2262.22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -580,7 +580,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>542.41</v>
+        <v>608.17</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -588,7 +588,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>417.16</v>
+        <v>1665.19</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -596,7 +596,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>1304.46</v>
+        <v>420.94</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -604,7 +604,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>3776.20</v>
+        <v>1794.54</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>791.10</v>
+        <v>1404.80</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>316.32</v>
+        <v>417.16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -628,7 +628,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>2392.64</v>
+        <v>581.46</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -636,7 +636,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>110.82</v>
+        <v>604.40</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -644,7 +644,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1071.60</v>
+        <v>9001.98</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -652,7 +652,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>1721.51</v>
+        <v>3382.30</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -660,7 +660,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>2262.22</v>
+        <v>1519.74</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -668,7 +668,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>608.17</v>
+        <v>1551.51</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -676,7 +676,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>1665.19</v>
+        <v>331.00</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -684,7 +684,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>420.94</v>
+        <v>5573.19</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -692,7 +692,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>1532.66</v>
+        <v>2949.30</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -700,7 +700,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>4455.39</v>
+        <v>542.41</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -708,7 +708,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>1857.06</v>
+        <v>417.16</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -716,7 +716,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>712.19</v>
+        <v>1304.46</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -724,7 +724,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>1026.59</v>
+        <v>6333.86</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -732,7 +732,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>125.29</v>
+        <v>294.88</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -740,7 +740,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>1215.98</v>
+        <v>1862.08</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -748,7 +748,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>6333.86</v>
+        <v>1544.56</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -756,7 +756,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>294.88</v>
+        <v>1532.66</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -764,7 +764,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>1862.08</v>
+        <v>4455.39</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -772,7 +772,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>1544.56</v>
+        <v>1857.06</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -780,7 +780,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>9001.98</v>
+        <v>712.19</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -788,7 +788,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>3382.30</v>
+        <v>1026.59</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -796,7 +796,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>1519.74</v>
+        <v>125.29</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -804,7 +804,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>1551.51</v>
+        <v>1215.98</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -812,7 +812,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>331.00</v>
+        <v>1538.46</v>
       </c>
     </row>
   </sheetData>
